--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pva/work/github.com/doclang-project/doclang-standard/reference/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A814EF-C50D-004B-948D-8458FD1A3094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5F33BA-4BB4-1B4A-9E0B-B0223A046B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="2" xr2:uid="{53E75A16-C0D6-3446-9F63-761042DEAA14}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{53E75A16-C0D6-3446-9F63-761042DEAA14}"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="180">
   <si>
     <t>{"read_only", "fillable"}</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Element</t>
-  </si>
-  <si>
-    <t>Includes doc-level metadata.</t>
   </si>
   <si>
     <t>Exists exactly once, as root element.</t>
@@ -424,9 +421,6 @@
     <t>special</t>
   </si>
   <si>
-    <t>grouping</t>
-  </si>
-  <si>
     <t>component head</t>
   </si>
   <si>
@@ -487,9 +481,6 @@
     <t>Formatting elements modify the styling and presentation within semantic or other formatting elements.</t>
   </si>
   <si>
-    <t>Structural elements define boundaries within tabular content (`&lt;otsl&gt;`).</t>
-  </si>
-  <si>
     <t>This category comprises elements with specialized document-level function.</t>
   </si>
   <si>
@@ -505,18 +496,10 @@
     <t>[Content] Raw text</t>
   </si>
   <si>
-    <t>Grouping elements enable the encapsulation of semantic elements or other grouping elements. Any grouping element may optionally begin with a [component head](#component-head-elements).</t>
-  </si>
-  <si>
     <t>Element Allowed Context</t>
   </si>
   <si>
     <t>Element Description</t>
-  </si>
-  <si>
-    <t>The component head is a sequence comprising the following elements in this order, whereby all elements are optional:&lt;br /&gt;&lt;ul&gt;&lt;li&gt;`&lt;thread&gt;`&lt;/li&gt;&lt;li&gt;`&lt;h_thread&gt;`&lt;/li&gt;&lt;li&gt;`&lt;meta&gt;`&lt;/li&gt;&lt;li&gt;sequence of 2*N `&lt;location&gt;`s (N&gt;1)&lt;/li&gt;&lt;li&gt;sequence of `&lt;timestamp&gt;`s&lt;/li&gt;&lt;li&gt;`&lt;layer&gt;`&lt;/li&gt;&lt;/ul&gt;
-A component head can only appear as the leading content of a semantic or grouping element, or also of `&lt;otsl&gt;` in the context of "implicit `&lt;text&gt;`s".&lt;br/&gt;
-The various component head elements are further specified in the following subsections.</t>
   </si>
   <si>
     <t>Any context that allows raw text content.</t>
@@ -593,6 +576,17 @@
   </si>
   <si>
     <t>The DocLang specification version the document is supposed to validate against, in "MAJOR.MINOR" format, i.e. first two positions of Semantic Verisoning.</t>
+  </si>
+  <si>
+    <t>The component head is a sequence comprising the following elements in this order, whereby all elements are optional:&lt;br /&gt;&lt;ul&gt;&lt;li&gt;`&lt;thread&gt;`&lt;/li&gt;&lt;li&gt;`&lt;h_thread&gt;`&lt;/li&gt;&lt;li&gt;`&lt;meta&gt;`&lt;/li&gt;&lt;li&gt;sequence of 2*N `&lt;location&gt;`s (N&gt;1)&lt;/li&gt;&lt;li&gt;sequence of `&lt;timestamp&gt;`s&lt;/li&gt;&lt;li&gt;`&lt;layer&gt;`&lt;/li&gt;&lt;/ul&gt;
+A component head can only appear as the leading content of a semantic element.
+The various component head elements are further specified in the following subsections.</t>
+  </si>
+  <si>
+    <t>Structural elements define boundaries within explicitly structured components like tables and lists.</t>
+  </si>
+  <si>
+    <t>Includes doc-level metadata. Also discussed in Appendix B.</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD32FCC-87C5-AA40-8339-205A5A3F17B2}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1009,74 +1003,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
         <v>121</v>
-      </c>
-      <c r="B1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="102" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>156</v>
+      <c r="B5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1106,62 +1092,62 @@
         <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="B3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="6" t="b">
         <v>1</v>
@@ -1178,16 +1164,16 @@
     </row>
     <row r="4" spans="1:8" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="b">
         <v>0</v>
@@ -1204,16 +1190,16 @@
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" s="6" t="b">
         <v>1</v>
@@ -1230,14 +1216,14 @@
     </row>
     <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E6" s="6" t="b">
         <v>1</v>
@@ -1254,14 +1240,14 @@
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>1</v>
@@ -1278,14 +1264,14 @@
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E8" s="6" t="b">
         <v>1</v>
@@ -1302,14 +1288,14 @@
     </row>
     <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E9" s="6" t="b">
         <v>1</v>
@@ -1326,14 +1312,14 @@
     </row>
     <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E10" s="6" t="b">
         <v>1</v>
@@ -1350,16 +1336,16 @@
     </row>
     <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E11" s="6" t="b">
         <v>1</v>
@@ -1376,16 +1362,16 @@
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E12" s="6" t="b">
         <v>1</v>
@@ -1402,16 +1388,16 @@
     </row>
     <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E13" s="6" t="b">
         <v>1</v>
@@ -1428,14 +1414,14 @@
     </row>
     <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E14" s="6" t="b">
         <v>1</v>
@@ -1452,14 +1438,14 @@
     </row>
     <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E15" s="6" t="b">
         <v>1</v>
@@ -1476,14 +1462,14 @@
     </row>
     <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E16" s="6" t="b">
         <v>1</v>
@@ -1500,14 +1486,14 @@
     </row>
     <row r="17" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>1</v>
@@ -1524,16 +1510,16 @@
     </row>
     <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E18" s="6" t="b">
         <v>1</v>
@@ -1550,14 +1536,14 @@
     </row>
     <row r="19" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="6" t="b">
         <v>1</v>
@@ -1574,16 +1560,16 @@
     </row>
     <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="6" t="b">
         <v>1</v>
@@ -1600,16 +1586,16 @@
     </row>
     <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="6" t="b">
         <v>1</v>
@@ -1626,16 +1612,16 @@
     </row>
     <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="6" t="b">
         <v>1</v>
@@ -1652,16 +1638,16 @@
     </row>
     <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" s="6" t="b">
         <v>1</v>
@@ -1678,16 +1664,16 @@
     </row>
     <row r="24" spans="1:8" ht="153" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E24" s="6" t="b">
         <v>0</v>
@@ -1704,16 +1690,16 @@
     </row>
     <row r="25" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E25" s="6" t="b">
         <v>0</v>
@@ -1730,16 +1716,16 @@
     </row>
     <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E26" s="6" t="b">
         <v>1</v>
@@ -1756,16 +1742,16 @@
     </row>
     <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E27" s="6" t="b">
         <v>1</v>
@@ -1782,16 +1768,16 @@
     </row>
     <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E28" s="6" t="b">
         <v>0</v>
@@ -1808,16 +1794,16 @@
     </row>
     <row r="29" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E29" s="6" t="b">
         <v>1</v>
@@ -1834,14 +1820,14 @@
     </row>
     <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E30" s="6" t="b">
         <v>0</v>
@@ -1858,14 +1844,14 @@
     </row>
     <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E31" s="6" t="b">
         <v>0</v>
@@ -1882,14 +1868,14 @@
     </row>
     <row r="32" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E32" s="6" t="b">
         <v>0</v>
@@ -1906,14 +1892,14 @@
     </row>
     <row r="33" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E33" s="6" t="b">
         <v>0</v>
@@ -1930,14 +1916,14 @@
     </row>
     <row r="34" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E34" s="6" t="b">
         <v>0</v>
@@ -1954,14 +1940,14 @@
     </row>
     <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="b">
         <v>1</v>
@@ -1978,14 +1964,14 @@
     </row>
     <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" s="6" t="b">
         <v>1</v>
@@ -2002,16 +1988,16 @@
     </row>
     <row r="37" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="6" t="b">
         <v>1</v>
@@ -2028,14 +2014,14 @@
     </row>
     <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E38" s="6" t="b">
         <v>0</v>
@@ -2052,14 +2038,14 @@
     </row>
     <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E39" s="6" t="b">
         <v>1</v>
@@ -2076,14 +2062,14 @@
     </row>
     <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E40" s="6" t="b">
         <v>1</v>
@@ -2100,14 +2086,14 @@
     </row>
     <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E41" s="6" t="b">
         <v>1</v>
@@ -2124,14 +2110,14 @@
     </row>
     <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E42" s="6" t="b">
         <v>1</v>
@@ -2148,14 +2134,14 @@
     </row>
     <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E43" s="6" t="b">
         <v>1</v>
@@ -2172,14 +2158,14 @@
     </row>
     <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E44" s="6" t="b">
         <v>1</v>
@@ -2196,14 +2182,14 @@
     </row>
     <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E45" s="6" t="b">
         <v>1</v>
@@ -2220,14 +2206,14 @@
     </row>
     <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E46" s="6" t="b">
         <v>1</v>
@@ -2244,16 +2230,16 @@
     </row>
     <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E47" s="6" t="b">
         <v>1</v>
@@ -2270,16 +2256,16 @@
     </row>
     <row r="48" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E48" s="6" t="b">
         <v>1</v>
@@ -2296,14 +2282,14 @@
     </row>
     <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E49" s="6" t="b">
         <v>0</v>
@@ -2320,14 +2306,14 @@
     </row>
     <row r="50" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E50" s="6" t="b">
         <v>0</v>
@@ -2344,14 +2330,14 @@
     </row>
     <row r="51" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E51" s="6" t="b">
         <v>0</v>
@@ -2368,14 +2354,14 @@
     </row>
     <row r="52" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E52" s="6" t="b">
         <v>0</v>
@@ -2392,14 +2378,14 @@
     </row>
     <row r="53" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E53" s="6" t="b">
         <v>0</v>
@@ -2416,14 +2402,14 @@
     </row>
     <row r="54" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E54" s="6" t="b">
         <v>0</v>
@@ -2440,14 +2426,14 @@
     </row>
     <row r="55" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E55" s="6" t="b">
         <v>0</v>
@@ -2464,14 +2450,14 @@
     </row>
     <row r="56" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E56" s="6" t="b">
         <v>0</v>
@@ -2488,14 +2474,14 @@
     </row>
     <row r="57" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E57" s="6" t="b">
         <v>0</v>
@@ -2512,14 +2498,14 @@
     </row>
     <row r="58" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E58" s="6" t="b">
         <v>0</v>
@@ -2536,16 +2522,16 @@
     </row>
     <row r="59" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E59" s="6" t="b">
         <v>1</v>
@@ -2557,15 +2543,15 @@
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>5</v>
@@ -2588,10 +2574,10 @@
     </row>
     <row r="61" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>5</v>
@@ -2614,10 +2600,10 @@
     </row>
     <row r="62" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>5</v>
@@ -2640,10 +2626,10 @@
     </row>
     <row r="63" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>5</v>
@@ -2666,10 +2652,10 @@
     </row>
     <row r="64" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>5</v>
@@ -2692,10 +2678,10 @@
     </row>
     <row r="65" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>5</v>
@@ -2718,10 +2704,10 @@
     </row>
     <row r="66" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>5</v>
@@ -2744,10 +2730,10 @@
     </row>
     <row r="67" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>5</v>
@@ -2770,10 +2756,10 @@
     </row>
     <row r="68" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>5</v>
@@ -2796,10 +2782,10 @@
     </row>
     <row r="69" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>5</v>
@@ -2822,10 +2808,10 @@
     </row>
     <row r="70" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>5</v>
@@ -2848,10 +2834,10 @@
     </row>
     <row r="71" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>5</v>
@@ -2874,10 +2860,10 @@
     </row>
     <row r="72" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>5</v>
@@ -2900,10 +2886,10 @@
     </row>
     <row r="73" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>5</v>
@@ -2926,10 +2912,10 @@
     </row>
     <row r="74" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>5</v>
@@ -2952,10 +2938,10 @@
     </row>
     <row r="75" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>5</v>
@@ -2978,10 +2964,10 @@
     </row>
     <row r="76" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -3036,145 +3022,145 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
       <c r="D1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" t="s">
         <v>112</v>
-      </c>
-      <c r="E1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -3182,13 +3168,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
@@ -3196,13 +3182,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -3210,13 +3196,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
         <v>1</v>
@@ -3224,27 +3210,27 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
         <v>2</v>
@@ -3252,33 +3238,33 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
